--- a/stories/arbres/TREE-SOC-003.xlsx
+++ b/stories/arbres/TREE-SOC-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est au parc, avec maman. Un boulanger est passé ce matin. Il a fait le pain. Un geste utile. Maman dit : boulanger, c'est un métier. La maîtresse aide à apprendre. Un métier. Un geste utile. Tom écoute. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
+          <t>Tom est au parc, avec maman. Un boulanger est passé ce matin. Il a fait le pain. Un geste utile. Boulanger, c'est un métier. La maîtresse aide à apprendre. Un métier. Un geste utile. Tom écoute. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est au parc, avec maman. Un boulanger est passé ce matin. Il a fait le pain. Un geste utile.
+maman|Boulanger, c'est un métier.
+narrateur|La maîtresse aide à apprendre. Un métier. Un geste utile. Tom écoute. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom prend le ballon. Maman dit : le chauffeur conduit le bus. C'est un métier. Un geste utile. Tom répète : chauffeur. On nomme un métier. On dit un geste utile.</t>
+          <t>Tom prend le ballon. Le chauffeur conduit le bus. C'est un métier. Un geste utile. Tom répète : chauffeur. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend le ballon.
+maman|Le chauffeur conduit le bus. C'est un métier.
+narrateur|Un geste utile. Tom répète : chauffeur. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le boulanger fait le pain. C'est un quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a nommé un métier. Boulanger. Geste utile : le pain. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2229,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2207,7 +2258,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers Tom. Le bois sent le chaud. Tom joue. Maman dit : chauffeur, métier, geste utile. Le bus avance. On nomme un métier. On dit un geste utile.</t>
+          <t>Tom va vers Tom. Le bois sent le chaud. Tom joue. Chauffeur, métier, geste utile. Le bus avance. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2345,6 +2396,13 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Tom. Le bois sent le chaud. Tom joue.
+maman|Chauffeur, métier, geste utile.
+narrateur|Le bus avance. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2589,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2756,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La lumière est claire. On essuie une miette. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2923,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3090,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On met le doudou près. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3257,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3424,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un chat miaule une fois. On lace les chaussures. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3591,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3758,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Léa. La couverture est douce. Léa écoute. Maîtresse, métier. Geste utile : lire. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3949,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3978,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Les chaussures font toc toc. On met le manteau. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Les chaussures font toc toc. On met le manteau. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4116,12 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Les chaussures font toc toc. On met le manteau. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4284,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4451,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La couverture est douce. On boit une gorgée. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4618,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4785,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Une cloche tinte au loin. On feuillette le livre. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4952,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5119,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Sami. Le bois sent le chaud. Sami mime le boulanger. Métier. Geste utile. Le pain. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5310,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5477,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le bois sent le chaud. On referme le livre. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5644,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5811,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On pose le ballon. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5978,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6145,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon sent la fleur. On secoue le sable. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6312,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6341,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom prend le seau. Maman dit : le médecin écoute le cœur. Métier. Geste utile. Tom pose le seau. Tom dit : médecin. On nomme un métier. On dit un geste utile.</t>
+          <t>Tom prend le seau. Le médecin écoute le cœur. Métier. Geste utile. Tom pose le seau. Médecin. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6479,14 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend le seau.
+maman|Le médecin écoute le cœur. Métier. Geste utile.
+narrateur|Tom pose le seau.
+enfant-m|Médecin. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6667,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Le médecin écoute le cœur. Quel geste ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6840,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Médecin. Geste utile. Tom a dit le métier. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6841,6 +7033,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7005,6 +7202,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Tom. Le vent est doux sur la joue. Tom et Tom roulent le ballon. Chauffeur. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7393,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7215,7 +7422,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Le tissu est tout doux. On caresse le tissu. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Le tissu est tout doux. On caresse le tissu. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7353,6 +7560,12 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le tissu est tout doux. On caresse le tissu. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7728,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7895,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une cuillère tinte. On tend la main. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8062,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8229,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le sable est tiède. On chante un petit air. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8396,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8563,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Léa. Un pigeon roucoule. Léa dit médecin. Geste utile. Tom répète le métier. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8754,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8921,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un rire court, tout petit. On compte jusqu'à trois. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9088,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9255,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On montre du doigt. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9422,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9589,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On range la chaise. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9756,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9923,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Sami. La terre est un peu humide. Sami range. Maman nomme encore un métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10114,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9855,7 +10143,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Un pigeon roucoule. On range un objet. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Un pigeon roucoule. On range un objet. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9993,6 +10281,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un pigeon roucoule. On range un objet. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10449,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10616,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On se tient la main. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10783,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10950,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On dit merci. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11117,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11284,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom prend le doudou. Maman parle de la maîtresse. Elle lit une histoire. Métier. Geste utile. Tom sourit. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11465,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|La maîtresse aide. C'est un quoi ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11638,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Maîtresse. Tom retient : métier, geste utile. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11497,6 +11831,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11661,6 +12000,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Tom. Un pigeon roucoule. Tom s'assoit. Boulanger. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11847,6 +12191,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12009,6 +12358,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La corde du sac est rêche. On souffle doucement. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12171,6 +12525,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12333,6 +12692,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On écoute jusqu'au bout. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12495,6 +12859,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12657,6 +13026,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un ruisseau chante. On attend son tour. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12819,6 +13193,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12981,6 +13360,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Léa. La fenêtre vibre un peu. Léa sourit. Maîtresse. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13167,6 +13551,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13191,7 +13580,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. La laine gratte un peu. On sourit ensemble. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. La laine gratte un peu. On sourit ensemble. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13329,6 +13718,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La laine gratte un peu. On sourit ensemble. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13491,6 +13886,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13653,6 +14053,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Un pain croustille. On pose les pieds par terre. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13815,6 +14220,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13977,6 +14387,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon glisse. On parle tout bas. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14139,6 +14554,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14301,6 +14721,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers Sami. Une cloche tinte au loin. Sami tapote. Médecin. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14487,6 +14912,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14649,6 +15079,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Une plume vole. On range les jouets. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14811,6 +15246,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14973,6 +15413,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le banc est lisse. On s'assoit un moment. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15135,6 +15580,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15297,6 +15747,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un grelot sonne. On respire, un, deux. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15459,6 +15914,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15477,7 +15937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15508,6 +15968,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-003.xlsx
+++ b/stories/arbres/TREE-SOC-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,11 @@
 narrateur|La maîtresse aide à apprendre. Un métier. Un geste utile. Tom écoute. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1526,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1696,7 @@
 narrateur|Un geste utile. Tom répète : chauffeur. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1880,7 @@
           <t>narrateur|Le boulanger fait le pain. C'est un quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2052,7 @@
           <t>narrateur|Tom a nommé un métier. Boulanger. Geste utile : le pain. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2248,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2403,6 +2418,7 @@
 narrateur|Le bus avance. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2594,6 +2610,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2761,6 +2778,7 @@
           <t>narrateur|Voilà le matin. La lumière est claire. On essuie une miette. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2928,6 +2946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3095,6 +3114,7 @@
           <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On met le doudou près. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3262,6 +3282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3429,6 +3450,7 @@
           <t>narrateur|Voilà le soir. Un chat miaule une fois. On lace les chaussures. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3596,6 +3618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3763,6 +3786,7 @@
           <t>narrateur|Tom va vers Léa. La couverture est douce. Léa écoute. Maîtresse, métier. Geste utile : lire. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3978,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4122,6 +4147,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4289,6 +4315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4456,6 +4483,7 @@
           <t>narrateur|Voilà après la sieste. La couverture est douce. On boit une gorgée. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4623,6 +4651,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4790,6 +4819,7 @@
           <t>narrateur|Voilà le soir. Une cloche tinte au loin. On feuillette le livre. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4957,6 +4987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5124,6 +5155,7 @@
           <t>narrateur|Tom va vers Sami. Le bois sent le chaud. Sami mime le boulanger. Métier. Geste utile. Le pain. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5315,6 +5347,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5482,6 +5515,7 @@
           <t>narrateur|Voilà le matin. Le bois sent le chaud. On referme le livre. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5649,6 +5683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5816,6 +5851,7 @@
           <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On pose le ballon. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5983,6 +6019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6150,6 +6187,7 @@
           <t>narrateur|Voilà le soir. Le savon sent la fleur. On secoue le sable. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6317,6 +6355,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6526,7 @@
 enfant-m|Médecin. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6674,6 +6714,7 @@
           <t>narrateur|Le médecin écoute le cœur. Quel geste ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6845,6 +6886,7 @@
           <t>narrateur|Médecin. Geste utile. Tom a dit le métier. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7082,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7250,7 @@
           <t>narrateur|Tom va vers Tom. Le vent est doux sur la joue. Tom et Tom roulent le ballon. Chauffeur. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7398,6 +7442,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7566,6 +7611,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7733,6 +7779,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7900,6 +7947,7 @@
           <t>narrateur|Voilà après la sieste. Une cuillère tinte. On tend la main. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8067,6 +8115,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8234,6 +8283,7 @@
           <t>narrateur|Voilà le soir. Le sable est tiède. On chante un petit air. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8401,6 +8451,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8568,6 +8619,7 @@
           <t>narrateur|Tom va vers Léa. Un pigeon roucoule. Léa dit médecin. Geste utile. Tom répète le métier. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8759,6 +8811,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8926,6 +8979,7 @@
           <t>narrateur|Voilà le matin. Un rire court, tout petit. On compte jusqu'à trois. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9093,6 +9147,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9260,6 +9315,7 @@
           <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On montre du doigt. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9427,6 +9483,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9594,6 +9651,7 @@
           <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On range la chaise. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9761,6 +9819,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9928,6 +9987,7 @@
           <t>narrateur|Tom va vers Sami. La terre est un peu humide. Sami range. Maman nomme encore un métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10119,6 +10179,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10287,6 +10348,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10454,6 +10516,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10621,6 +10684,7 @@
           <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On se tient la main. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10788,6 +10852,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10955,6 +11020,7 @@
           <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On dit merci. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11122,6 +11188,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11289,6 +11356,7 @@
           <t>narrateur|Tom prend le doudou. Maman parle de la maîtresse. Elle lit une histoire. Métier. Geste utile. Tom sourit. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11472,6 +11540,7 @@
           <t>narrateur|La maîtresse aide. C'est un quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11643,6 +11712,7 @@
           <t>narrateur|Maîtresse. Tom retient : métier, geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11838,6 +11908,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12005,6 +12076,7 @@
           <t>narrateur|Tom va vers Tom. Un pigeon roucoule. Tom s'assoit. Boulanger. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12196,6 +12268,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12363,6 +12436,7 @@
           <t>narrateur|Voilà le matin. La corde du sac est rêche. On souffle doucement. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12530,6 +12604,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12697,6 +12772,7 @@
           <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On écoute jusqu'au bout. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12864,6 +12940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13031,6 +13108,7 @@
           <t>narrateur|Voilà le soir. Un ruisseau chante. On attend son tour. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13198,6 +13276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13365,6 +13444,7 @@
           <t>narrateur|Tom va vers Léa. La fenêtre vibre un peu. Léa sourit. Maîtresse. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13556,6 +13636,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13724,6 +13805,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13891,6 +13973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14058,6 +14141,7 @@
           <t>narrateur|Voilà après la sieste. Un pain croustille. On pose les pieds par terre. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. On souffle. Tom sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14225,6 +14309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14392,6 +14477,7 @@
           <t>narrateur|Voilà le soir. Le savon glisse. On parle tout bas. On a nommé un métier. On a dit un geste utile. Chauffeur, conduire. On nomme un métier. On dit un geste utile. Tom prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14559,6 +14645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14726,6 +14813,7 @@
           <t>narrateur|Tom va vers Sami. Une cloche tinte au loin. Sami tapote. Médecin. Métier. Geste utile. On nomme un métier. On dit un geste utile.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14917,6 +15005,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15084,6 +15173,7 @@
           <t>narrateur|Voilà le matin. Une plume vole. On range les jouets. On a nommé un métier. On a dit un geste utile. Boulanger, le pain. On nomme un métier. On dit un geste utile. Tom dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15251,6 +15341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15418,6 +15509,7 @@
           <t>narrateur|Voilà après la sieste. Le banc est lisse. On s'assoit un moment. On a nommé un métier. On a dit un geste utile. Médecin, écouter. On nomme un métier. On dit un geste utile. Maman serre Tom tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15585,6 +15677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15752,6 +15845,7 @@
           <t>narrateur|Voilà le soir. Un grelot sonne. On respire, un, deux. On a nommé un métier. On a dit un geste utile. Maîtresse, lire. On nomme un métier. On dit un geste utile. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15919,6 +16013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15937,7 +16032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15975,6 +16070,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15989,7 +16098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16176,6 +16285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
